--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -29332,7 +29332,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -31107,7 +31107,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
@@ -31117,12 +31117,12 @@
       </c>
       <c r="H454" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I454" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J454" s="3" t="inlineStr">
@@ -31132,12 +31132,12 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M454" s="3" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="N454" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31597,7 +31597,7 @@
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G461" s="3" t="inlineStr">
@@ -31607,12 +31607,12 @@
       </c>
       <c r="H461" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I461" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J461" s="3" t="inlineStr">
@@ -31622,12 +31622,12 @@
       </c>
       <c r="K461" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L461" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M461" s="3" t="inlineStr">
@@ -31637,7 +31637,7 @@
       </c>
       <c r="N461" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32087,7 +32087,7 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G468" s="3" t="inlineStr">
@@ -32097,12 +32097,12 @@
       </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I468" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J468" s="3" t="inlineStr">
@@ -32112,12 +32112,12 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M468" s="3" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="N468" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35453,38 +35453,30 @@
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H517" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I517" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H517" s="5" t="n">
+        <v>15121000</v>
+      </c>
+      <c r="I517" s="5" t="n">
+        <v>30922</v>
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K517" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L517" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K517" s="5" t="n">
+        <v>15121000</v>
+      </c>
+      <c r="L517" s="5" t="n">
+        <v>30922</v>
       </c>
       <c r="M517" s="3" t="inlineStr">
         <is>
@@ -35493,7 +35485,7 @@
       </c>
       <c r="N517" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35935,38 +35927,30 @@
       </c>
       <c r="F524" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H524" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I524" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H524" s="5" t="n">
+        <v>15046000</v>
+      </c>
+      <c r="I524" s="5" t="n">
+        <v>30769</v>
       </c>
       <c r="J524" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K524" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L524" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K524" s="5" t="n">
+        <v>15046000</v>
+      </c>
+      <c r="L524" s="5" t="n">
+        <v>30769</v>
       </c>
       <c r="M524" s="3" t="inlineStr">
         <is>
@@ -35975,7 +35959,7 @@
       </c>
       <c r="N524" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36417,7 +36401,7 @@
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
@@ -36427,12 +36411,12 @@
       </c>
       <c r="H531" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I531" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J531" s="3" t="inlineStr">
@@ -36442,12 +36426,12 @@
       </c>
       <c r="K531" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L531" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M531" s="3" t="inlineStr">
@@ -36457,7 +36441,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36899,7 +36883,7 @@
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
@@ -36909,12 +36893,12 @@
       </c>
       <c r="H538" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I538" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J538" s="3" t="inlineStr">
@@ -36924,12 +36908,12 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M538" s="3" t="inlineStr">
@@ -36939,7 +36923,7 @@
       </c>
       <c r="N538" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37381,7 +37365,7 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -37391,12 +37375,12 @@
       </c>
       <c r="H545" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I545" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J545" s="3" t="inlineStr">
@@ -37406,12 +37390,12 @@
       </c>
       <c r="K545" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L545" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M545" s="3" t="inlineStr">
@@ -37421,7 +37405,7 @@
       </c>
       <c r="N545" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38835,38 +38819,30 @@
       </c>
       <c r="F566" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H566" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I566" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H566" s="5" t="n">
+        <v>14528000</v>
+      </c>
+      <c r="I566" s="5" t="n">
+        <v>29710</v>
       </c>
       <c r="J566" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K566" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L566" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K566" s="5" t="n">
+        <v>14528000</v>
+      </c>
+      <c r="L566" s="5" t="n">
+        <v>29710</v>
       </c>
       <c r="M566" s="3" t="inlineStr">
         <is>
@@ -38875,7 +38851,7 @@
       </c>
       <c r="N566" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38905,38 +38881,30 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H567" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I567" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="n">
+        <v>12943000</v>
+      </c>
+      <c r="I567" s="5" t="n">
+        <v>28698</v>
       </c>
       <c r="J567" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K567" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L567" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K567" s="5" t="n">
+        <v>12943000</v>
+      </c>
+      <c r="L567" s="5" t="n">
+        <v>28698</v>
       </c>
       <c r="M567" s="3" t="inlineStr">
         <is>
@@ -38945,7 +38913,7 @@
       </c>
       <c r="N567" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39317,38 +39285,30 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H573" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I573" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="n">
+        <v>14455000</v>
+      </c>
+      <c r="I573" s="5" t="n">
+        <v>29560</v>
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K573" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L573" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K573" s="5" t="n">
+        <v>14455000</v>
+      </c>
+      <c r="L573" s="5" t="n">
+        <v>29560</v>
       </c>
       <c r="M573" s="3" t="inlineStr">
         <is>
@@ -39357,7 +39317,7 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39387,38 +39347,30 @@
       </c>
       <c r="F574" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H574" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I574" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H574" s="5" t="n">
+        <v>12878000</v>
+      </c>
+      <c r="I574" s="5" t="n">
+        <v>28554</v>
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K574" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L574" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K574" s="5" t="n">
+        <v>12878000</v>
+      </c>
+      <c r="L574" s="5" t="n">
+        <v>28554</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
@@ -39427,7 +39379,7 @@
       </c>
       <c r="N574" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39869,7 +39821,7 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
@@ -39879,12 +39831,12 @@
       </c>
       <c r="H581" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I581" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J581" s="3" t="inlineStr">
@@ -39894,12 +39846,12 @@
       </c>
       <c r="K581" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L581" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M581" s="3" t="inlineStr">
@@ -39909,7 +39861,7 @@
       </c>
       <c r="N581" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40351,7 +40303,7 @@
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
@@ -40361,12 +40313,12 @@
       </c>
       <c r="H588" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I588" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J588" s="3" t="inlineStr">
@@ -40376,12 +40328,12 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M588" s="3" t="inlineStr">
@@ -40391,7 +40343,7 @@
       </c>
       <c r="N588" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41245,7 +41197,7 @@
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
@@ -41255,12 +41207,12 @@
       </c>
       <c r="H601" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I601" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J601" s="3" t="inlineStr">
@@ -41270,12 +41222,12 @@
       </c>
       <c r="K601" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L601" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M601" s="3" t="inlineStr">
@@ -41285,7 +41237,7 @@
       </c>
       <c r="N601" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41727,7 +41679,7 @@
       </c>
       <c r="F608" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G608" s="3" t="inlineStr">
@@ -41737,12 +41689,12 @@
       </c>
       <c r="H608" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I608" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J608" s="3" t="inlineStr">
@@ -41752,12 +41704,12 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M608" s="3" t="inlineStr">
@@ -41767,7 +41719,7 @@
       </c>
       <c r="N608" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42209,38 +42161,30 @@
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H615" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I615" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="n">
+        <v>13815000</v>
+      </c>
+      <c r="I615" s="5" t="n">
+        <v>28252</v>
       </c>
       <c r="J615" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K615" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L615" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K615" s="5" t="n">
+        <v>13815000</v>
+      </c>
+      <c r="L615" s="5" t="n">
+        <v>28252</v>
       </c>
       <c r="M615" s="3" t="inlineStr">
         <is>
@@ -42249,7 +42193,7 @@
       </c>
       <c r="N615" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42691,38 +42635,30 @@
       </c>
       <c r="F622" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H622" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I622" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H622" s="5" t="n">
+        <v>13678000</v>
+      </c>
+      <c r="I622" s="5" t="n">
+        <v>27971</v>
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K622" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L622" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K622" s="5" t="n">
+        <v>13678000</v>
+      </c>
+      <c r="L622" s="5" t="n">
+        <v>27971</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
@@ -42731,7 +42667,7 @@
       </c>
       <c r="N622" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43173,7 +43109,7 @@
       </c>
       <c r="F629" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G629" s="3" t="inlineStr">
@@ -43183,12 +43119,12 @@
       </c>
       <c r="H629" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I629" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J629" s="3" t="inlineStr">
@@ -43198,12 +43134,12 @@
       </c>
       <c r="K629" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L629" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M629" s="3" t="inlineStr">
@@ -43213,7 +43149,7 @@
       </c>
       <c r="N629" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43655,7 +43591,7 @@
       </c>
       <c r="F636" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G636" s="3" t="inlineStr">
@@ -43665,12 +43601,12 @@
       </c>
       <c r="H636" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I636" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J636" s="3" t="inlineStr">
@@ -43680,12 +43616,12 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M636" s="3" t="inlineStr">
@@ -43695,7 +43631,7 @@
       </c>
       <c r="N636" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -47823,7 +47759,7 @@
           <t>A | 548呎 (2房)
 $1401万
 $25,573/呎
-(26年-08月-02日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -47997,7 +47933,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48007,7 +47943,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48017,7 +47953,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>148</t>
         </is>
       </c>
     </row>
@@ -48203,12 +48139,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -48266,12 +48202,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -48329,12 +48265,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -48770,12 +48706,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1512万
+$30,922/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -48833,12 +48769,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1505万
+$30,769/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -48896,12 +48832,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -48959,12 +48895,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -49022,12 +48958,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -49203,20 +49139,20 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
+$1294万
+$28,698/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1453万
+$29,710/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -49266,20 +49202,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
+$1288万
+$28,554/呎
+(26年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1446万
+$29,560/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -49329,12 +49265,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -49392,12 +49328,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -49526,12 +49462,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -49589,12 +49525,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -49652,12 +49588,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1382万
+$28,252/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -49715,12 +49651,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1368万
+$27,971/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -49778,12 +49714,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -49841,12 +49777,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -26496,7 +26496,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -29801,7 +29801,7 @@
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -29809,31 +29809,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H435" s="5" t="n">
-        <v>18394000</v>
-      </c>
-      <c r="I435" s="5" t="n">
-        <v>35856</v>
+      <c r="H435" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I435" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K435" s="5" t="n">
-        <v>16186720</v>
-      </c>
-      <c r="L435" s="5" t="n">
-        <v>31553</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K435" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L435" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N435" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32709,7 +32717,7 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
@@ -32717,31 +32725,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H477" s="5" t="n">
-        <v>17241000</v>
-      </c>
-      <c r="I477" s="5" t="n">
-        <v>33608</v>
+      <c r="H477" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I477" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K477" s="5" t="n">
-        <v>15172080</v>
-      </c>
-      <c r="L477" s="5" t="n">
-        <v>29575</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K477" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L477" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N477" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33525,7 +33541,7 @@
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G489" s="3" t="inlineStr">
@@ -33535,12 +33551,12 @@
       </c>
       <c r="H489" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I489" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J489" s="3" t="inlineStr">
@@ -33550,12 +33566,12 @@
       </c>
       <c r="K489" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L489" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M489" s="3" t="inlineStr">
@@ -33565,7 +33581,7 @@
       </c>
       <c r="N489" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34007,7 +34023,7 @@
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr">
@@ -34017,12 +34033,12 @@
       </c>
       <c r="H496" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I496" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J496" s="3" t="inlineStr">
@@ -34032,12 +34048,12 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M496" s="3" t="inlineStr">
@@ -34047,7 +34063,7 @@
       </c>
       <c r="N496" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34489,7 +34505,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -34499,12 +34515,12 @@
       </c>
       <c r="H503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J503" s="3" t="inlineStr">
@@ -34514,12 +34530,12 @@
       </c>
       <c r="K503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M503" s="3" t="inlineStr">
@@ -34529,7 +34545,7 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34971,7 +34987,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -34981,12 +34997,12 @@
       </c>
       <c r="H510" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I510" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J510" s="3" t="inlineStr">
@@ -34996,12 +35012,12 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M510" s="3" t="inlineStr">
@@ -35011,7 +35027,7 @@
       </c>
       <c r="N510" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37435,7 +37451,7 @@
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -37445,12 +37461,12 @@
       </c>
       <c r="H546" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I546" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J546" s="3" t="inlineStr">
@@ -37460,12 +37476,12 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M546" s="3" t="inlineStr">
@@ -37475,7 +37491,7 @@
       </c>
       <c r="N546" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38337,7 +38353,7 @@
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G559" s="3" t="inlineStr">
@@ -38347,12 +38363,12 @@
       </c>
       <c r="H559" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I559" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J559" s="3" t="inlineStr">
@@ -38362,12 +38378,12 @@
       </c>
       <c r="K559" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L559" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M559" s="3" t="inlineStr">
@@ -38377,7 +38393,7 @@
       </c>
       <c r="N559" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38407,7 +38423,7 @@
       </c>
       <c r="F560" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G560" s="3" t="inlineStr">
@@ -38417,12 +38433,12 @@
       </c>
       <c r="H560" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I560" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J560" s="3" t="inlineStr">
@@ -38432,12 +38448,12 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M560" s="3" t="inlineStr">
@@ -38447,7 +38463,7 @@
       </c>
       <c r="N560" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39751,7 +39767,7 @@
       </c>
       <c r="F580" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G580" s="3" t="inlineStr">
@@ -39761,12 +39777,12 @@
       </c>
       <c r="H580" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I580" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J580" s="3" t="inlineStr">
@@ -39776,12 +39792,12 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M580" s="3" t="inlineStr">
@@ -39791,7 +39807,7 @@
       </c>
       <c r="N580" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40233,7 +40249,7 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
@@ -40243,12 +40259,12 @@
       </c>
       <c r="H587" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I587" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J587" s="3" t="inlineStr">
@@ -40258,12 +40274,12 @@
       </c>
       <c r="K587" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L587" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M587" s="3" t="inlineStr">
@@ -40273,7 +40289,7 @@
       </c>
       <c r="N587" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40715,7 +40731,7 @@
       </c>
       <c r="F594" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G594" s="3" t="inlineStr">
@@ -40725,12 +40741,12 @@
       </c>
       <c r="H594" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I594" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J594" s="3" t="inlineStr">
@@ -40740,12 +40756,12 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M594" s="3" t="inlineStr">
@@ -40755,7 +40771,7 @@
       </c>
       <c r="N594" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -47374,7 +47390,7 @@
           <t>A | 548呎 (2房)
 $1496万
 $27,299/呎
-(26年-08月-23日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -47933,12 +47949,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -47953,7 +47969,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -48053,12 +48069,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
-$1839万
-$35,856/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -48431,12 +48447,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
-$1724万
-$33,608/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -48454,12 +48470,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -48517,12 +48533,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -48580,12 +48596,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -48643,12 +48659,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -48950,12 +48966,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -49076,20 +49092,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -49273,12 +49289,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -49336,12 +49352,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -49399,12 +49415,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -32717,38 +32717,30 @@
       </c>
       <c r="F477" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H477" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I477" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H477" s="5" t="n">
+        <v>16064000</v>
+      </c>
+      <c r="I477" s="5" t="n">
+        <v>31314</v>
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K477" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L477" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K477" s="5" t="n">
+        <v>16064000</v>
+      </c>
+      <c r="L477" s="5" t="n">
+        <v>31314</v>
       </c>
       <c r="M477" s="3" t="inlineStr">
         <is>
@@ -32757,7 +32749,7 @@
       </c>
       <c r="N477" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36899,38 +36891,30 @@
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H538" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I538" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H538" s="5" t="n">
+        <v>14897000</v>
+      </c>
+      <c r="I538" s="5" t="n">
+        <v>30464</v>
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K538" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L538" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K538" s="5" t="n">
+        <v>14897000</v>
+      </c>
+      <c r="L538" s="5" t="n">
+        <v>30464</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
@@ -36939,7 +36923,7 @@
       </c>
       <c r="N538" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37381,38 +37365,30 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H545" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I545" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H545" s="5" t="n">
+        <v>15159000</v>
+      </c>
+      <c r="I545" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="J545" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K545" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L545" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K545" s="5" t="n">
+        <v>15159000</v>
+      </c>
+      <c r="L545" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="M545" s="3" t="inlineStr">
         <is>
@@ -37421,7 +37397,7 @@
       </c>
       <c r="N545" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40249,38 +40225,30 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H587" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I587" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H587" s="5" t="n">
+        <v>14310000</v>
+      </c>
+      <c r="I587" s="5" t="n">
+        <v>29264</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K587" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L587" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K587" s="5" t="n">
+        <v>14310000</v>
+      </c>
+      <c r="L587" s="5" t="n">
+        <v>29264</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
@@ -40289,7 +40257,7 @@
       </c>
       <c r="N587" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42713,38 +42681,30 @@
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H623" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I623" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H623" s="5" t="n">
+        <v>12186000</v>
+      </c>
+      <c r="I623" s="5" t="n">
+        <v>27020</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K623" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L623" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K623" s="5" t="n">
+        <v>12186000</v>
+      </c>
+      <c r="L623" s="5" t="n">
+        <v>27020</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -42753,7 +42713,7 @@
       </c>
       <c r="N623" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -47949,7 +47909,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47959,7 +47919,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48447,12 +48407,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
-招标单位
--
-(在售)</t>
+$1606万
+$31,314/呎
+(26年-09月-13日)</t>
         </is>
       </c>
     </row>
@@ -48911,12 +48871,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1490万
+$30,464/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -48974,12 +48934,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1516万
+$31,000/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -49352,12 +49312,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1431万
+$29,264/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -49659,12 +49619,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1219万
+$27,020/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -41663,38 +41663,30 @@
       </c>
       <c r="F608" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H608" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I608" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H608" s="5" t="n">
+        <v>13955000</v>
+      </c>
+      <c r="I608" s="5" t="n">
+        <v>28538</v>
       </c>
       <c r="J608" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K608" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L608" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K608" s="5" t="n">
+        <v>13955000</v>
+      </c>
+      <c r="L608" s="5" t="n">
+        <v>28538</v>
       </c>
       <c r="M608" s="3" t="inlineStr">
         <is>
@@ -41703,7 +41695,7 @@
       </c>
       <c r="N608" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -47909,7 +47901,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47919,7 +47911,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -49501,12 +49493,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1396万
+$28,538/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -35466,7 +35466,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -48679,7 +48679,7 @@
           <t>B | 489呎 (2房)
 $1512万
 $30,922/呎
-(26年-09月-06日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>7084000</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>22207</v>
+        <v>22138</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>7084000</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>22207</v>
+        <v>22138</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -35940,7 +35940,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -40287,38 +40287,30 @@
       </c>
       <c r="F588" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H588" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I588" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H588" s="5" t="n">
+        <v>12750000</v>
+      </c>
+      <c r="I588" s="5" t="n">
+        <v>28271</v>
       </c>
       <c r="J588" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K588" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L588" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K588" s="5" t="n">
+        <v>12750000</v>
+      </c>
+      <c r="L588" s="5" t="n">
+        <v>28271</v>
       </c>
       <c r="M588" s="3" t="inlineStr">
         <is>
@@ -40327,7 +40319,7 @@
       </c>
       <c r="N588" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42142,7 +42134,7 @@
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H615" s="5" t="n">
@@ -42199,38 +42191,30 @@
       </c>
       <c r="F616" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H616" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I616" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="n">
+        <v>12309000</v>
+      </c>
+      <c r="I616" s="5" t="n">
+        <v>27293</v>
       </c>
       <c r="J616" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K616" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L616" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K616" s="5" t="n">
+        <v>12309000</v>
+      </c>
+      <c r="L616" s="5" t="n">
+        <v>27293</v>
       </c>
       <c r="M616" s="3" t="inlineStr">
         <is>
@@ -42239,7 +42223,7 @@
       </c>
       <c r="N616" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -45883,9 +45867,9 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>C | 319呎 (1房)
+          <t>C | 320呎 (1房)
 $708万
-$22,207/呎
+$22,138/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -47452,7 +47436,7 @@
           <t>A | 548呎 (2房)
 $1481万
 $27,029/呎
-(26年-08月-25日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -47901,7 +47885,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47911,7 +47895,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48742,7 +48726,7 @@
           <t>B | 489呎 (2房)
 $1505万
 $30,769/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -49175,7 +49159,7 @@
           <t>A | 451呎 (2房)
 $1288万
 $28,554/呎
-(26年-09月-04日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -49296,12 +49280,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1275万
+$28,271/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -49548,12 +49532,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1231万
+$27,293/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -49561,7 +49545,7 @@
           <t>B | 489呎 (2房)
 $1382万
 $28,252/呎
-(26年-09月-04日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -123,13 +123,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
@@ -279,10 +279,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1057,31 +1057,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>13763000</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>31933</v>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>12111440</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>28101</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7069,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7071,12 +7079,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -7086,12 +7094,12 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -7101,7 +7109,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19479,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -19481,12 +19489,12 @@
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I284" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J284" s="3" t="inlineStr">
@@ -19496,12 +19504,12 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
@@ -19511,7 +19519,7 @@
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19891,7 +19899,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -19901,12 +19909,12 @@
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J290" s="3" t="inlineStr">
@@ -19916,12 +19924,12 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
@@ -19931,7 +19939,7 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24027,7 +24035,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -24037,12 +24045,12 @@
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J350" s="3" t="inlineStr">
@@ -24052,12 +24060,12 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M350" s="3" t="inlineStr">
@@ -24067,7 +24075,7 @@
       </c>
       <c r="N350" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24439,7 +24447,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -24449,12 +24457,12 @@
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -24464,12 +24472,12 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M356" s="3" t="inlineStr">
@@ -24479,7 +24487,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32235,7 +32243,7 @@
       </c>
       <c r="F470" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G470" s="3" t="inlineStr">
@@ -32243,31 +32251,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H470" s="5" t="n">
-        <v>17414000</v>
-      </c>
-      <c r="I470" s="5" t="n">
-        <v>33945</v>
+      <c r="H470" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I470" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K470" s="5" t="n">
-        <v>15324320</v>
-      </c>
-      <c r="L470" s="5" t="n">
-        <v>29872</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L470" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38816,7 +38832,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -41717,7 +41733,7 @@
       </c>
       <c r="F609" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G609" s="3" t="inlineStr">
@@ -41727,12 +41743,12 @@
       </c>
       <c r="H609" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I609" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J609" s="3" t="inlineStr">
@@ -41742,12 +41758,12 @@
       </c>
       <c r="K609" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L609" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M609" s="3" t="inlineStr">
@@ -41757,7 +41773,7 @@
       </c>
       <c r="N609" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43131,7 +43147,7 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
@@ -43141,12 +43157,12 @@
       </c>
       <c r="H630" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I630" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J630" s="3" t="inlineStr">
@@ -43156,12 +43172,12 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M630" s="3" t="inlineStr">
@@ -43171,7 +43187,7 @@
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43613,7 +43629,7 @@
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G637" s="3" t="inlineStr">
@@ -43623,12 +43639,12 @@
       </c>
       <c r="H637" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I637" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J637" s="3" t="inlineStr">
@@ -43638,12 +43654,12 @@
       </c>
       <c r="K637" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L637" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M637" s="3" t="inlineStr">
@@ -43653,7 +43669,7 @@
       </c>
       <c r="N637" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43734,12 +43750,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -43754,7 +43770,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -43829,12 +43845,12 @@
       <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 431呎 (2房)
-$1376万
-$31,933/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $1452万
@@ -43890,7 +43906,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 319呎 (1房)
 $990万
@@ -43898,7 +43914,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 431呎 (2房)
 $1356万
@@ -43906,7 +43922,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $1430万
@@ -43969,7 +43985,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 319呎 (1房)
 $980万
@@ -43977,7 +43993,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 431呎 (2房)
 招标单位
@@ -43985,7 +44001,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -44040,7 +44056,7 @@
 (25年-09月-03日)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 818呎 (3房)
 招标单位
@@ -44048,7 +44064,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 319呎 (1房)
 $970万
@@ -44064,7 +44080,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -44135,7 +44151,7 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 431呎 (2房)
 招标单位
@@ -44143,7 +44159,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $1388万
@@ -44301,7 +44317,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $1361万
@@ -44380,7 +44396,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $1347万
@@ -44593,12 +44609,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 818呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
@@ -44617,7 +44633,7 @@
 (26年-03月-10日)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -44696,7 +44712,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -44775,7 +44791,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -44854,7 +44870,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 招标单位
@@ -46154,7 +46170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46174,7 +46190,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -46229,7 +46245,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 $1488万
@@ -46284,7 +46300,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 $1466万
@@ -46339,7 +46355,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46386,15 +46402,15 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46441,15 +46457,15 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46504,7 +46520,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 $1409万
@@ -46559,7 +46575,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 $1395万
@@ -46614,7 +46630,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 $1381万
@@ -46661,7 +46677,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
@@ -46669,7 +46685,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46826,7 +46842,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
@@ -46834,7 +46850,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46889,7 +46905,7 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
 招标单位
@@ -46991,12 +47007,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -47046,12 +47062,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -47266,7 +47282,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
@@ -47510,7 +47526,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 315呎 (1房)
 -
@@ -47596,7 +47612,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
@@ -47761,7 +47777,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
 招标单位
@@ -47885,12 +47901,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -47905,7 +47921,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -48005,7 +48021,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
 招标单位
@@ -48068,7 +48084,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
 $1812万
@@ -48091,7 +48107,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48131,7 +48147,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
 $1794万
@@ -48146,7 +48162,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -48154,7 +48170,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48194,7 +48210,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
 招标单位
@@ -48209,7 +48225,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -48217,7 +48233,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48257,7 +48273,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
 招标单位
@@ -48323,9 +48339,9 @@
       <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 513呎 (2房)
-$1741万
-$33,945/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -48406,7 +48422,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48469,7 +48485,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48532,7 +48548,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48595,7 +48611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48650,7 +48666,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -48713,7 +48729,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -48784,7 +48800,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -48902,7 +48918,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -49028,7 +49044,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -49036,7 +49052,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -49104,7 +49120,7 @@
           <t>B | 489呎 (2房)
 $1453万
 $29,710/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -49217,7 +49233,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
 招标单位
@@ -49225,7 +49241,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -49351,7 +49367,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -49414,7 +49430,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -49469,12 +49485,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -49658,15 +49674,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位
@@ -49721,15 +49737,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
 招标单位

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -7069,38 +7069,30 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>37758000</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>46159</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K97" s="5" t="n">
+        <v>37758000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>46159</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7109,7 +7101,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32738,7 +32730,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -37386,7 +37378,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -38894,7 +38886,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -39829,38 +39821,30 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H581" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I581" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H581" s="5" t="n">
+        <v>12814000</v>
+      </c>
+      <c r="I581" s="5" t="n">
+        <v>28412</v>
       </c>
       <c r="J581" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K581" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L581" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K581" s="5" t="n">
+        <v>12814000</v>
+      </c>
+      <c r="L581" s="5" t="n">
+        <v>28412</v>
       </c>
       <c r="M581" s="3" t="inlineStr">
         <is>
@@ -39869,7 +39853,7 @@
       </c>
       <c r="N581" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40246,7 +40230,7 @@
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H587" s="5" t="n">
@@ -41676,7 +41660,7 @@
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H608" s="5" t="n">
@@ -42616,7 +42600,7 @@
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H622" s="5" t="n">
@@ -43147,38 +43131,30 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="I630" s="5" t="n">
+        <v>26614</v>
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K630" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="L630" s="5" t="n">
+        <v>26614</v>
       </c>
       <c r="M630" s="3" t="inlineStr">
         <is>
@@ -43187,7 +43163,7 @@
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43750,7 +43726,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43760,7 +43736,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44609,12 +44585,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 818呎 (3房)
-招标单位
--
-(在售)</t>
+$3776万
+$46,159/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
@@ -47901,7 +47877,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47911,7 +47887,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48404,7 +48380,7 @@
           <t>G | 513呎 (2房)
 $1606万
 $31,314/呎
-(26年-09月-13日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -48931,7 +48907,7 @@
           <t>B | 489呎 (2房)
 $1516万
 $31,000/呎
-(26年-09月-11日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -49112,7 +49088,7 @@
           <t>A | 451呎 (2房)
 $1294万
 $28,698/呎
-(26年-09月-06日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -49233,12 +49209,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1281万
+$28,412/呎
+(26年-10月-04日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -49309,7 +49285,7 @@
           <t>B | 489呎 (2房)
 $1431万
 $29,264/呎
-(26年-09月-13日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -49498,7 +49474,7 @@
           <t>B | 489呎 (2房)
 $1396万
 $28,538/呎
-(26年-09月-15日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -49624,7 +49600,7 @@
           <t>B | 489呎 (2房)
 $1368万
 $27,971/呎
-(26年-09月-04日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -49674,12 +49650,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1200万
+$26,614/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -8669,38 +8669,30 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>12183000</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>26894</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K121" s="5" t="n">
+        <v>12183000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>26894</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8709,7 +8701,7 @@
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26079,38 +26071,30 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H380" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I380" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H380" s="5" t="n">
+        <v>15036000</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>27438</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K380" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L380" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K380" s="5" t="n">
+        <v>15036000</v>
+      </c>
+      <c r="L380" s="5" t="n">
+        <v>27438</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
@@ -26119,7 +26103,7 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39290,7 +39274,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -43131,30 +43115,38 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="H630" s="5" t="n">
-        <v>12003000</v>
-      </c>
-      <c r="I630" s="5" t="n">
-        <v>26614</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H630" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I630" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K630" s="5" t="n">
-        <v>12003000</v>
-      </c>
-      <c r="L630" s="5" t="n">
-        <v>26614</v>
+      <c r="K630" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L630" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M630" s="3" t="inlineStr">
         <is>
@@ -43163,7 +43155,7 @@
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43726,7 +43718,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43736,7 +43728,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44846,12 +44838,12 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
+$1218万
+$26,894/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -46146,7 +46138,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46156,7 +46148,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47258,12 +47250,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1504万
+$27,438/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -47877,7 +47869,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47887,7 +47879,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -49159,7 +49151,7 @@
           <t>B | 489呎 (2房)
 $1446万
 $29,560/呎
-(26年-09月-05日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -49650,12 +49642,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-$1200万
-$26,614/呎
-(26年-09月-29日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -24431,38 +24431,30 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H356" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I356" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>15418000</v>
+      </c>
+      <c r="I356" s="5" t="n">
+        <v>28135</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K356" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L356" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K356" s="5" t="n">
+        <v>15418000</v>
+      </c>
+      <c r="L356" s="5" t="n">
+        <v>28135</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -24471,7 +24463,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28495,38 +28487,30 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H416" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>14371000</v>
+      </c>
+      <c r="I416" s="5" t="n">
+        <v>26224</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K416" s="5" t="n">
+        <v>14371000</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>26224</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -28535,7 +28519,7 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36401,38 +36385,30 @@
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H531" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I531" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H531" s="5" t="n">
+        <v>14971000</v>
+      </c>
+      <c r="I531" s="5" t="n">
+        <v>30616</v>
       </c>
       <c r="J531" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K531" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L531" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K531" s="5" t="n">
+        <v>14971000</v>
+      </c>
+      <c r="L531" s="5" t="n">
+        <v>30616</v>
       </c>
       <c r="M531" s="3" t="inlineStr">
         <is>
@@ -36441,7 +36417,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36888,7 +36864,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -41701,38 +41677,30 @@
       </c>
       <c r="F609" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H609" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I609" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H609" s="5" t="n">
+        <v>12433000</v>
+      </c>
+      <c r="I609" s="5" t="n">
+        <v>27568</v>
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K609" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L609" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K609" s="5" t="n">
+        <v>12433000</v>
+      </c>
+      <c r="L609" s="5" t="n">
+        <v>27568</v>
       </c>
       <c r="M609" s="3" t="inlineStr">
         <is>
@@ -41741,7 +41709,7 @@
       </c>
       <c r="N609" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42646,7 +42614,7 @@
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H623" s="5" t="n">
@@ -43045,38 +43013,30 @@
       </c>
       <c r="F629" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H629" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I629" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H629" s="5" t="n">
+        <v>13472000</v>
+      </c>
+      <c r="I629" s="5" t="n">
+        <v>27550</v>
       </c>
       <c r="J629" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K629" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L629" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K629" s="5" t="n">
+        <v>13472000</v>
+      </c>
+      <c r="L629" s="5" t="n">
+        <v>27550</v>
       </c>
       <c r="M629" s="3" t="inlineStr">
         <is>
@@ -43085,7 +43045,7 @@
       </c>
       <c r="N629" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43115,38 +43075,30 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="I630" s="5" t="n">
+        <v>26614</v>
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K630" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="L630" s="5" t="n">
+        <v>26614</v>
       </c>
       <c r="M630" s="3" t="inlineStr">
         <is>
@@ -43155,7 +43107,7 @@
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46138,7 +46090,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46148,7 +46100,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47030,12 +46982,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1542万
+$28,135/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -47580,12 +47532,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1437万
+$26,224/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -47869,7 +47821,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47879,7 +47831,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48768,12 +48720,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1497万
+$30,616/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -48836,7 +48788,7 @@
           <t>B | 489呎 (2房)
 $1490万
 $30,464/呎
-(26年-09月-11日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -49453,12 +49405,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
+$1243万
+$27,568/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -49584,7 +49536,7 @@
           <t>A | 451呎 (2房)
 $1219万
 $27,020/呎
-(26年-09月-11日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -49642,20 +49594,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="inlineStr">
+$1200万
+$26,614/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1347万
+$27,550/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4515,31 +4515,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n">
-        <v>13607000</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>30038</v>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>11974160</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>26433</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5105,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5105,31 +5113,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>13473000</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>29742</v>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>11856240</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>26173</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21073,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -21065,31 +21081,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H307" s="5" t="n">
-        <v>13814000</v>
-      </c>
-      <c r="I307" s="5" t="n">
-        <v>30766</v>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I307" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K307" s="5" t="n">
-        <v>12156320</v>
-      </c>
-      <c r="L307" s="5" t="n">
-        <v>27074</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N307" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21143,7 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -21129,12 +21153,12 @@
       </c>
       <c r="H308" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I308" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J308" s="3" t="inlineStr">
@@ -21144,12 +21168,12 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M308" s="3" t="inlineStr">
@@ -21159,7 +21183,7 @@
       </c>
       <c r="N308" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23607,7 +23631,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -23617,12 +23641,12 @@
       </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I344" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J344" s="3" t="inlineStr">
@@ -23632,12 +23656,12 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M344" s="3" t="inlineStr">
@@ -23647,7 +23671,7 @@
       </c>
       <c r="N344" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40721,7 +40745,7 @@
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G595" s="3" t="inlineStr">
@@ -40731,12 +40755,12 @@
       </c>
       <c r="H595" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I595" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J595" s="3" t="inlineStr">
@@ -40746,12 +40770,12 @@
       </c>
       <c r="K595" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L595" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M595" s="3" t="inlineStr">
@@ -40761,7 +40785,7 @@
       </c>
       <c r="N595" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -41203,7 +41227,7 @@
       </c>
       <c r="F602" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G602" s="3" t="inlineStr">
@@ -41213,12 +41237,12 @@
       </c>
       <c r="H602" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I602" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J602" s="3" t="inlineStr">
@@ -41228,12 +41252,12 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M602" s="3" t="inlineStr">
@@ -41243,7 +41267,7 @@
       </c>
       <c r="N602" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -43670,12 +43694,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -44237,12 +44261,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1361万
-$30,038/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -44316,12 +44340,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1347万
-$29,742/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -46090,12 +46114,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -46110,7 +46134,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -46542,20 +46566,20 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 449呎 (2房)
-$1381万
-$30,766/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -46872,12 +46896,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -47821,7 +47845,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47841,7 +47865,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -49279,12 +49303,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -49342,12 +49366,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">

--- a/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第1A期/维港．湾畔第1A期_销控明细表.xlsx
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8690,14 +8690,14 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
         <v>12183000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>26894</v>
+        <v>26954</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>12183000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>26894</v>
+        <v>26954</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -29723,38 +29723,30 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H434" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I434" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H434" s="5" t="n">
+        <v>13804000</v>
+      </c>
+      <c r="I434" s="5" t="n">
+        <v>25190</v>
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K434" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L434" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K434" s="5" t="n">
+        <v>13804000</v>
+      </c>
+      <c r="L434" s="5" t="n">
+        <v>25190</v>
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
@@ -29763,7 +29755,7 @@
       </c>
       <c r="N434" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38321,38 +38313,30 @@
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H559" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I559" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H559" s="5" t="n">
+        <v>14601000</v>
+      </c>
+      <c r="I559" s="5" t="n">
+        <v>29859</v>
       </c>
       <c r="J559" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K559" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L559" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K559" s="5" t="n">
+        <v>14601000</v>
+      </c>
+      <c r="L559" s="5" t="n">
+        <v>29859</v>
       </c>
       <c r="M559" s="3" t="inlineStr">
         <is>
@@ -38361,7 +38345,7 @@
       </c>
       <c r="N559" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39794,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -40276,7 +40260,7 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
@@ -41157,38 +41141,30 @@
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H601" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I601" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H601" s="5" t="n">
+        <v>14167000</v>
+      </c>
+      <c r="I601" s="5" t="n">
+        <v>28971</v>
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K601" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L601" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K601" s="5" t="n">
+        <v>14167000</v>
+      </c>
+      <c r="L601" s="5" t="n">
+        <v>28971</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
@@ -41197,7 +41173,7 @@
       </c>
       <c r="N601" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41227,38 +41203,30 @@
       </c>
       <c r="F602" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G602" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H602" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I602" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H602" s="5" t="n">
+        <v>12623000</v>
+      </c>
+      <c r="I602" s="5" t="n">
+        <v>27989</v>
       </c>
       <c r="J602" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K602" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L602" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K602" s="5" t="n">
+        <v>12623000</v>
+      </c>
+      <c r="L602" s="5" t="n">
+        <v>27989</v>
       </c>
       <c r="M602" s="3" t="inlineStr">
         <is>
@@ -41267,7 +41235,7 @@
       </c>
       <c r="N602" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42172,7 +42140,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -44558,7 +44526,7 @@
           <t>B | 818呎 (3房)
 $3776万
 $46,159/呎
-(26年-10月-02日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
@@ -44816,10 +44784,10 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>E | 453呎 (2房)
+          <t>E | 452呎 (2房)
 $1218万
-$26,894/呎
-(26年-10月-06日)</t>
+$26,954/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -46114,7 +46082,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -46124,7 +46092,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47721,12 +47689,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
+$1380万
+$25,190/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -47845,7 +47813,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -47855,7 +47823,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -48996,12 +48964,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1460万
+$29,859/呎
+(26年-10月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -49182,7 +49150,7 @@
           <t>A | 451呎 (2房)
 $1281万
 $28,412/呎
-(26年-10月-04日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -49245,7 +49213,7 @@
           <t>A | 451呎 (2房)
 $1275万
 $28,271/呎
-(26年-09月-24日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -49366,20 +49334,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>A | 451呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
+$1262万
+$27,989/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-招标单位
--
-(在售)</t>
+$1417万
+$28,971/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -49497,7 +49465,7 @@
           <t>A | 451呎 (2房)
 $1231万
 $27,293/呎
-(26年-09月-21日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
